--- a/Datasets/udepo_uranium_deposits.xlsx
+++ b/Datasets/udepo_uranium_deposits.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UDepo Data List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDepo Data List" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J161"/>
+  <dimension ref="A2:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="1.71428571428571" customWidth="1" min="1" max="1"/>
@@ -715,11 +715,6 @@
           <t>Grade Range</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>record_source</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="B10" s="15" t="inlineStr">
@@ -760,11 +755,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="15" t="inlineStr">
@@ -805,11 +795,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="15" t="inlineStr">
@@ -850,11 +835,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="15" t="inlineStr">
@@ -895,11 +875,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="15" t="inlineStr">
@@ -940,11 +915,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="15" t="inlineStr">
@@ -985,11 +955,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="15" t="inlineStr">
@@ -1030,11 +995,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="15" t="inlineStr">
@@ -1075,11 +1035,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="B18" s="15" t="inlineStr">
@@ -1120,11 +1075,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="B19" s="15" t="inlineStr">
@@ -1165,11 +1115,6 @@
           <t>≥0.10 - &lt;0.20</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="15" t="inlineStr">
@@ -1210,11 +1155,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="15" t="inlineStr">
@@ -1255,11 +1195,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="B22" s="15" t="inlineStr">
@@ -1300,11 +1235,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="B23" s="15" t="inlineStr">
@@ -1345,11 +1275,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="B24" s="15" t="inlineStr">
@@ -1390,11 +1315,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="B25" s="15" t="inlineStr">
@@ -1435,11 +1355,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="B26" s="15" t="inlineStr">
@@ -1480,11 +1395,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="B27" s="15" t="inlineStr">
@@ -1525,11 +1435,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="B28" s="15" t="inlineStr">
@@ -1570,11 +1475,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="B29" s="15" t="inlineStr">
@@ -1615,11 +1515,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="B30" s="15" t="inlineStr">
@@ -1660,11 +1555,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="B31" s="15" t="inlineStr">
@@ -1705,11 +1595,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="B32" s="15" t="inlineStr">
@@ -1750,11 +1635,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="B33" s="15" t="inlineStr">
@@ -1795,11 +1675,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="B34" s="15" t="inlineStr">
@@ -1840,11 +1715,6 @@
           <t>≥0.10 - &lt;0.20</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="B35" s="15" t="inlineStr">
@@ -1885,11 +1755,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="B36" s="15" t="inlineStr">
@@ -1930,11 +1795,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="B37" s="15" t="inlineStr">
@@ -1975,11 +1835,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="B38" s="15" t="inlineStr">
@@ -2020,11 +1875,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="B39" s="15" t="inlineStr">
@@ -2065,11 +1915,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="B40" s="15" t="inlineStr">
@@ -2110,11 +1955,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="B41" s="15" t="inlineStr">
@@ -2155,11 +1995,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="B42" s="15" t="inlineStr">
@@ -2200,11 +2035,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="B43" s="15" t="inlineStr">
@@ -2245,11 +2075,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="B44" s="15" t="inlineStr">
@@ -2290,11 +2115,6 @@
           <t>&gt;0 - &lt;0.01</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="B45" s="15" t="inlineStr">
@@ -2335,11 +2155,6 @@
           <t>&gt;0 - &lt;0.01</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="B46" s="15" t="inlineStr">
@@ -2380,11 +2195,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="B47" s="15" t="inlineStr">
@@ -2425,11 +2235,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="B48" s="15" t="inlineStr">
@@ -2470,11 +2275,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="B49" s="15" t="inlineStr">
@@ -2515,11 +2315,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
       <c r="B50" s="15" t="inlineStr">
@@ -2560,11 +2355,6 @@
           <t>&gt;0 - &lt;0.01</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
       <c r="B51" s="15" t="inlineStr">
@@ -2605,11 +2395,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
       <c r="B52" s="15" t="inlineStr">
@@ -2650,11 +2435,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
       <c r="B53" s="15" t="inlineStr">
@@ -2695,11 +2475,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
       <c r="B54" s="15" t="inlineStr">
@@ -2740,11 +2515,6 @@
           <t>≥0.10 - &lt;0.20</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
       <c r="B55" s="15" t="inlineStr">
@@ -2785,11 +2555,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
       <c r="B56" s="15" t="inlineStr">
@@ -2830,11 +2595,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
       <c r="B57" s="15" t="inlineStr">
@@ -2875,11 +2635,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
       <c r="B58" s="15" t="inlineStr">
@@ -2920,11 +2675,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
       <c r="B59" s="15" t="inlineStr">
@@ -2965,11 +2715,6 @@
           <t>≥0.10 - &lt;0.20</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
       <c r="B60" s="15" t="inlineStr">
@@ -3010,11 +2755,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
       <c r="B61" s="15" t="inlineStr">
@@ -3055,11 +2795,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
       <c r="B62" s="15" t="inlineStr">
@@ -3100,11 +2835,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
       <c r="B63" s="15" t="inlineStr">
@@ -3145,11 +2875,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
       <c r="B64" s="15" t="inlineStr">
@@ -3190,11 +2915,6 @@
           <t>&gt;0 - &lt;0.01</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
       <c r="B65" s="15" t="inlineStr">
@@ -3235,11 +2955,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
       <c r="B66" s="15" t="inlineStr">
@@ -3280,11 +2995,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
       <c r="B67" s="15" t="inlineStr">
@@ -3325,11 +3035,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
       <c r="B68" s="15" t="inlineStr">
@@ -3370,11 +3075,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
       <c r="B69" s="15" t="inlineStr">
@@ -3415,11 +3115,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
       <c r="B70" s="15" t="inlineStr">
@@ -3460,11 +3155,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
       <c r="B71" s="15" t="inlineStr">
@@ -3505,11 +3195,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
       <c r="B72" s="15" t="inlineStr">
@@ -3550,11 +3235,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
       <c r="B73" s="15" t="inlineStr">
@@ -3595,11 +3275,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
       <c r="B74" s="15" t="inlineStr">
@@ -3640,11 +3315,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
       <c r="B75" s="15" t="inlineStr">
@@ -3685,11 +3355,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
       <c r="B76" s="15" t="inlineStr">
@@ -3730,11 +3395,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
       <c r="B77" s="15" t="inlineStr">
@@ -3775,11 +3435,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
       <c r="B78" s="15" t="inlineStr">
@@ -3820,11 +3475,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
       <c r="B79" s="15" t="inlineStr">
@@ -3865,11 +3515,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
       <c r="B80" s="15" t="inlineStr">
@@ -3910,11 +3555,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
       <c r="B81" s="15" t="inlineStr">
@@ -3955,11 +3595,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
       <c r="B82" s="15" t="inlineStr">
@@ -4000,11 +3635,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="83" ht="12.75" customHeight="1">
       <c r="B83" s="15" t="inlineStr">
@@ -4045,11 +3675,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="84" ht="12.75" customHeight="1">
       <c r="B84" s="15" t="inlineStr">
@@ -4090,11 +3715,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="85" ht="12.75" customHeight="1">
       <c r="B85" s="15" t="inlineStr">
@@ -4135,11 +3755,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
       <c r="B86" s="15" t="inlineStr">
@@ -4180,11 +3795,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
       <c r="B87" s="15" t="inlineStr">
@@ -4225,11 +3835,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
       <c r="B88" s="15" t="inlineStr">
@@ -4266,11 +3871,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
       <c r="B89" s="15" t="inlineStr">
@@ -4311,11 +3911,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="90" ht="12.75" customHeight="1">
       <c r="B90" s="15" t="inlineStr">
@@ -4356,11 +3951,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="91" ht="12.75" customHeight="1">
       <c r="B91" s="15" t="inlineStr">
@@ -4401,11 +3991,6 @@
           <t>≥0.01 - &lt;0.05</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="92" ht="12.75" customHeight="1">
       <c r="B92" s="15" t="inlineStr">
@@ -4446,11 +4031,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="93" ht="12.75" customHeight="1">
       <c r="B93" s="15" t="inlineStr">
@@ -4491,11 +4071,6 @@
           <t>≥0.05 - &lt;0.10</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="94" ht="12.75" customHeight="1">
       <c r="B94" s="15" t="inlineStr">
@@ -4528,11 +4103,6 @@
       </c>
       <c r="H94" s="15" t="n"/>
       <c r="I94" s="16" t="n"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="95" ht="12.75" customHeight="1">
       <c r="B95" s="15" t="inlineStr">
@@ -4565,11 +4135,6 @@
       </c>
       <c r="H95" s="15" t="n"/>
       <c r="I95" s="16" t="n"/>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="96" ht="12.75" customHeight="1">
       <c r="B96" s="15" t="inlineStr">
@@ -4602,11 +4167,6 @@
       </c>
       <c r="H96" s="15" t="n"/>
       <c r="I96" s="16" t="n"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="97" ht="12.75" customHeight="1">
       <c r="B97" s="15" t="inlineStr">
@@ -4639,11 +4199,6 @@
       </c>
       <c r="H97" s="15" t="n"/>
       <c r="I97" s="16" t="n"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="98" ht="12.75" customHeight="1">
       <c r="B98" s="15" t="inlineStr">
@@ -4676,11 +4231,6 @@
       </c>
       <c r="H98" s="15" t="n"/>
       <c r="I98" s="16" t="n"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="99" ht="12.75" customHeight="1">
       <c r="B99" s="15" t="inlineStr">
@@ -4713,11 +4263,6 @@
       </c>
       <c r="H99" s="15" t="n"/>
       <c r="I99" s="16" t="n"/>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="100" ht="12.75" customHeight="1">
       <c r="B100" s="15" t="inlineStr">
@@ -4750,11 +4295,6 @@
       </c>
       <c r="H100" s="15" t="n"/>
       <c r="I100" s="16" t="n"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="101" ht="12.75" customHeight="1">
       <c r="B101" s="15" t="inlineStr">
@@ -4787,11 +4327,6 @@
       </c>
       <c r="H101" s="15" t="n"/>
       <c r="I101" s="16" t="n"/>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="102" ht="12.75" customHeight="1">
       <c r="B102" s="15" t="inlineStr">
@@ -4824,11 +4359,6 @@
       </c>
       <c r="H102" s="15" t="n"/>
       <c r="I102" s="16" t="n"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="103" ht="12.75" customHeight="1">
       <c r="B103" s="15" t="inlineStr">
@@ -4861,11 +4391,6 @@
       </c>
       <c r="H103" s="15" t="n"/>
       <c r="I103" s="16" t="n"/>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="104" ht="12.75" customHeight="1">
       <c r="B104" s="15" t="inlineStr">
@@ -4898,11 +4423,6 @@
       </c>
       <c r="H104" s="15" t="n"/>
       <c r="I104" s="16" t="n"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="105" ht="12.75" customHeight="1">
       <c r="B105" s="15" t="inlineStr">
@@ -4935,11 +4455,6 @@
       </c>
       <c r="H105" s="15" t="n"/>
       <c r="I105" s="16" t="n"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="106" ht="12.75" customHeight="1">
       <c r="B106" s="15" t="inlineStr">
@@ -4972,11 +4487,6 @@
       </c>
       <c r="H106" s="15" t="n"/>
       <c r="I106" s="16" t="n"/>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="B107" s="15" t="inlineStr">
@@ -5009,11 +4519,6 @@
       </c>
       <c r="H107" s="15" t="n"/>
       <c r="I107" s="16" t="n"/>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="108" ht="12.75" customHeight="1">
       <c r="B108" s="15" t="inlineStr">
@@ -5046,11 +4551,6 @@
       </c>
       <c r="H108" s="15" t="n"/>
       <c r="I108" s="16" t="n"/>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="109" ht="12.75" customHeight="1">
       <c r="B109" s="15" t="inlineStr">
@@ -5083,11 +4583,6 @@
       </c>
       <c r="H109" s="15" t="n"/>
       <c r="I109" s="16" t="n"/>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="B110" s="15" t="inlineStr">
@@ -5120,11 +4615,6 @@
       </c>
       <c r="H110" s="15" t="n"/>
       <c r="I110" s="16" t="n"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="B111" s="15" t="inlineStr">
@@ -5157,11 +4647,6 @@
       </c>
       <c r="H111" s="15" t="n"/>
       <c r="I111" s="16" t="n"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="112" ht="12.75" customHeight="1">
       <c r="B112" s="15" t="inlineStr">
@@ -5194,11 +4679,6 @@
       </c>
       <c r="H112" s="15" t="n"/>
       <c r="I112" s="16" t="n"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="113" ht="12.75" customHeight="1">
       <c r="B113" s="15" t="inlineStr">
@@ -5231,11 +4711,6 @@
       </c>
       <c r="H113" s="15" t="n"/>
       <c r="I113" s="16" t="n"/>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="114" ht="12.75" customHeight="1">
       <c r="B114" s="15" t="inlineStr">
@@ -5268,11 +4743,6 @@
       </c>
       <c r="H114" s="15" t="n"/>
       <c r="I114" s="16" t="n"/>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="B115" s="15" t="inlineStr">
@@ -5305,11 +4775,6 @@
       </c>
       <c r="H115" s="15" t="n"/>
       <c r="I115" s="16" t="n"/>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="116" ht="12.75" customHeight="1">
       <c r="B116" s="15" t="inlineStr">
@@ -5342,11 +4807,6 @@
       </c>
       <c r="H116" s="15" t="n"/>
       <c r="I116" s="16" t="n"/>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="117" ht="12.75" customHeight="1">
       <c r="B117" s="15" t="inlineStr">
@@ -5379,11 +4839,6 @@
       </c>
       <c r="H117" s="15" t="n"/>
       <c r="I117" s="16" t="n"/>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="B118" s="15" t="inlineStr">
@@ -5416,11 +4871,6 @@
       </c>
       <c r="H118" s="15" t="n"/>
       <c r="I118" s="16" t="n"/>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="B119" s="15" t="inlineStr">
@@ -5453,11 +4903,6 @@
       </c>
       <c r="H119" s="15" t="n"/>
       <c r="I119" s="16" t="n"/>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="120" ht="12.75" customHeight="1">
       <c r="B120" s="15" t="inlineStr">
@@ -5490,11 +4935,6 @@
       </c>
       <c r="H120" s="15" t="n"/>
       <c r="I120" s="16" t="n"/>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="B121" s="15" t="inlineStr">
@@ -5527,11 +4967,6 @@
       </c>
       <c r="H121" s="15" t="n"/>
       <c r="I121" s="16" t="n"/>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="122" ht="12.75" customHeight="1">
       <c r="B122" s="15" t="inlineStr">
@@ -5564,11 +4999,6 @@
       </c>
       <c r="H122" s="15" t="n"/>
       <c r="I122" s="16" t="n"/>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="123" ht="12.75" customHeight="1">
       <c r="B123" s="15" t="inlineStr">
@@ -5601,11 +5031,6 @@
       </c>
       <c r="H123" s="15" t="n"/>
       <c r="I123" s="16" t="n"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="124" ht="12.75" customHeight="1">
       <c r="B124" s="15" t="inlineStr">
@@ -5638,11 +5063,6 @@
       </c>
       <c r="H124" s="15" t="n"/>
       <c r="I124" s="16" t="n"/>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="B125" s="15" t="inlineStr">
@@ -5675,11 +5095,6 @@
       </c>
       <c r="H125" s="15" t="n"/>
       <c r="I125" s="16" t="n"/>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="B126" s="15" t="inlineStr">
@@ -5712,11 +5127,6 @@
       </c>
       <c r="H126" s="15" t="n"/>
       <c r="I126" s="16" t="n"/>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="127" ht="12.75" customHeight="1">
       <c r="B127" s="15" t="inlineStr">
@@ -5749,11 +5159,6 @@
       </c>
       <c r="H127" s="15" t="n"/>
       <c r="I127" s="16" t="n"/>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="128" ht="12.75" customHeight="1">
       <c r="B128" s="15" t="inlineStr">
@@ -5786,11 +5191,6 @@
       </c>
       <c r="H128" s="15" t="n"/>
       <c r="I128" s="16" t="n"/>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="B129" s="15" t="inlineStr">
@@ -5823,11 +5223,6 @@
       </c>
       <c r="H129" s="15" t="n"/>
       <c r="I129" s="16" t="n"/>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="B130" s="15" t="inlineStr">
@@ -5860,11 +5255,6 @@
       </c>
       <c r="H130" s="15" t="n"/>
       <c r="I130" s="16" t="n"/>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="131" ht="12.75" customHeight="1">
       <c r="B131" s="15" t="inlineStr">
@@ -5897,11 +5287,6 @@
       </c>
       <c r="H131" s="15" t="n"/>
       <c r="I131" s="16" t="n"/>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="132" ht="12.75" customHeight="1">
       <c r="B132" s="15" t="inlineStr">
@@ -5934,11 +5319,6 @@
       </c>
       <c r="H132" s="15" t="n"/>
       <c r="I132" s="16" t="n"/>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="B133" s="15" t="inlineStr">
@@ -5971,11 +5351,6 @@
       </c>
       <c r="H133" s="15" t="n"/>
       <c r="I133" s="16" t="n"/>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="B134" s="15" t="inlineStr">
@@ -6008,11 +5383,6 @@
       </c>
       <c r="H134" s="15" t="n"/>
       <c r="I134" s="16" t="n"/>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="135" ht="12.75" customHeight="1">
       <c r="B135" s="15" t="inlineStr">
@@ -6045,11 +5415,6 @@
       </c>
       <c r="H135" s="15" t="n"/>
       <c r="I135" s="16" t="n"/>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="136" ht="12.75" customHeight="1">
       <c r="B136" s="15" t="inlineStr">
@@ -6082,11 +5447,6 @@
       </c>
       <c r="H136" s="15" t="n"/>
       <c r="I136" s="16" t="n"/>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="B137" s="15" t="inlineStr">
@@ -6119,11 +5479,6 @@
       </c>
       <c r="H137" s="15" t="n"/>
       <c r="I137" s="16" t="n"/>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="B138" s="15" t="inlineStr">
@@ -6156,11 +5511,6 @@
       </c>
       <c r="H138" s="15" t="n"/>
       <c r="I138" s="16" t="n"/>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="139" ht="12.75" customHeight="1">
       <c r="B139" s="15" t="inlineStr">
@@ -6193,11 +5543,6 @@
       </c>
       <c r="H139" s="15" t="n"/>
       <c r="I139" s="16" t="n"/>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="140" ht="12.75" customHeight="1">
       <c r="B140" s="15" t="inlineStr">
@@ -6230,11 +5575,6 @@
       </c>
       <c r="H140" s="15" t="n"/>
       <c r="I140" s="16" t="n"/>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="B141" s="15" t="inlineStr">
@@ -6267,11 +5607,6 @@
       </c>
       <c r="H141" s="15" t="n"/>
       <c r="I141" s="16" t="n"/>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="B142" s="15" t="inlineStr">
@@ -6304,11 +5639,6 @@
       </c>
       <c r="H142" s="15" t="n"/>
       <c r="I142" s="16" t="n"/>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="143" ht="12.75" customHeight="1">
       <c r="B143" s="15" t="inlineStr">
@@ -6341,11 +5671,6 @@
       </c>
       <c r="H143" s="15" t="n"/>
       <c r="I143" s="16" t="n"/>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="144" ht="12.75" customHeight="1">
       <c r="B144" s="15" t="inlineStr">
@@ -6378,11 +5703,6 @@
       </c>
       <c r="H144" s="15" t="n"/>
       <c r="I144" s="16" t="n"/>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="B145" s="15" t="inlineStr">
@@ -6415,11 +5735,6 @@
       </c>
       <c r="H145" s="15" t="n"/>
       <c r="I145" s="16" t="n"/>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="B146" s="15" t="inlineStr">
@@ -6452,11 +5767,6 @@
       </c>
       <c r="H146" s="15" t="n"/>
       <c r="I146" s="16" t="n"/>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="147" ht="12.75" customHeight="1">
       <c r="B147" s="15" t="inlineStr">
@@ -6489,11 +5799,6 @@
       </c>
       <c r="H147" s="15" t="n"/>
       <c r="I147" s="16" t="n"/>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="148" ht="12.75" customHeight="1">
       <c r="B148" s="15" t="inlineStr">
@@ -6526,11 +5831,6 @@
       </c>
       <c r="H148" s="15" t="n"/>
       <c r="I148" s="16" t="n"/>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="B149" s="15" t="inlineStr">
@@ -6563,11 +5863,6 @@
       </c>
       <c r="H149" s="15" t="n"/>
       <c r="I149" s="16" t="n"/>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="B150" s="15" t="inlineStr">
@@ -6600,11 +5895,6 @@
       </c>
       <c r="H150" s="15" t="n"/>
       <c r="I150" s="16" t="n"/>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="151" ht="12.75" customHeight="1">
       <c r="B151" s="15" t="inlineStr">
@@ -6637,11 +5927,6 @@
       </c>
       <c r="H151" s="15" t="n"/>
       <c r="I151" s="16" t="n"/>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="152" ht="12.75" customHeight="1">
       <c r="B152" s="15" t="inlineStr">
@@ -6674,11 +5959,6 @@
       </c>
       <c r="H152" s="15" t="n"/>
       <c r="I152" s="16" t="n"/>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="B153" s="15" t="inlineStr">
@@ -6711,11 +5991,6 @@
       </c>
       <c r="H153" s="15" t="n"/>
       <c r="I153" s="16" t="n"/>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="B154" s="15" t="inlineStr">
@@ -6748,11 +6023,6 @@
       </c>
       <c r="H154" s="15" t="n"/>
       <c r="I154" s="16" t="n"/>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="155" ht="12.75" customHeight="1">
       <c r="B155" s="13" t="inlineStr">
@@ -6785,14 +6055,8 @@
       </c>
       <c r="H155" s="13" t="n"/>
       <c r="I155" s="17" t="n"/>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
           <t>India</t>
@@ -6823,235 +6087,9 @@
           <t>deposit</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>0.05</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr"/>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>FIELD-231f2529</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>E2E Test Outcrop</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Field observation</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>deposit</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr"/>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>FIELD-708348d0</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>E2E Test Outcrop</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Field observation</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>deposit</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr"/>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>FIELD-8cff0af4</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>E2E Test Outcrop</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Field observation</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>deposit</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr"/>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>FIELD-b59ba75d</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>E2E Test Outcrop</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Field observation</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>deposit</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr"/>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>FIELD-6a17c1b1</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>E2E Test Outcrop</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Uranium</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Field observation</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>deposit</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>added</t>
         </is>
       </c>
     </row>
